--- a/artfynd/A 11965-2026 artfynd.xlsx
+++ b/artfynd/A 11965-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,6 +789,240 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>131775130</v>
+      </c>
+      <c r="B3" t="n">
+        <v>97284</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>291</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Stubbtrådmossa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Fuscocephaloziopsis catenulata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Huebener) Váňa &amp; L.Söderstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Staverud, Lysevattnets östsida, Dls</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>341517</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6521640</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Granskog med asp.</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>På asplåga. # Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>131775187</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97370</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1841</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vedflikmossa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lophozia guttulata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Staverud, Lysevattnets östsida, Dls</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>341555</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6521847</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Gammal granskog.</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>På grov granlåga. # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11965-2026 artfynd.xlsx
+++ b/artfynd/A 11965-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131773087</v>
       </c>
       <c r="B2" t="n">
-        <v>96471</v>
+        <v>96474</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>131775130</v>
       </c>
       <c r="B3" t="n">
-        <v>97284</v>
+        <v>97287</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>131775187</v>
       </c>
       <c r="B4" t="n">
-        <v>97370</v>
+        <v>97373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 11965-2026 artfynd.xlsx
+++ b/artfynd/A 11965-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131773087</v>
       </c>
       <c r="B2" t="n">
-        <v>96474</v>
+        <v>96480</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>131775130</v>
       </c>
       <c r="B3" t="n">
-        <v>97287</v>
+        <v>97293</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>131775187</v>
       </c>
       <c r="B4" t="n">
-        <v>97373</v>
+        <v>97379</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 11965-2026 artfynd.xlsx
+++ b/artfynd/A 11965-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1024,6 +1024,347 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>131988835</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80333</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Staverud, Lysevattnets östsida, Dls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>341593</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6521595</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Gammal granskog med mycket asp och en del grov tall.</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>skogslönn</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>På en mindre lönn. # Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>131988964</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97286</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>53</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Staverud, Lysevattnets östsida, Dls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>341634</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6521632</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Gammal granskog med mycket asp och en del grov tall.</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>På granlåga. # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131988965</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97510</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>232</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vedsäckmossa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Calypogeia suecica</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Arnell &amp; J.Perss.) Müll.Frib.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Staverud, Lysevattnets östsida, Dls</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>341641</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6521636</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Gammal granskog med mycket asp och en del grov tall.</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>På murken låga.</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11965-2026 artfynd.xlsx
+++ b/artfynd/A 11965-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131773087</v>
       </c>
       <c r="B2" t="n">
-        <v>96480</v>
+        <v>96483</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>131775130</v>
       </c>
       <c r="B3" t="n">
-        <v>97293</v>
+        <v>97296</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>131775187</v>
       </c>
       <c r="B4" t="n">
-        <v>97379</v>
+        <v>97382</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>131988835</v>
       </c>
       <c r="B5" t="n">
-        <v>80333</v>
+        <v>80334</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>131988964</v>
       </c>
       <c r="B6" t="n">
-        <v>97286</v>
+        <v>97287</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>131988965</v>
       </c>
       <c r="B7" t="n">
-        <v>97510</v>
+        <v>97511</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 11965-2026 artfynd.xlsx
+++ b/artfynd/A 11965-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131773087</v>
       </c>
       <c r="B2" t="n">
-        <v>96483</v>
+        <v>96488</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>131775130</v>
       </c>
       <c r="B3" t="n">
-        <v>97296</v>
+        <v>97301</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>131775187</v>
       </c>
       <c r="B4" t="n">
-        <v>97382</v>
+        <v>97387</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>131988835</v>
       </c>
       <c r="B5" t="n">
-        <v>80334</v>
+        <v>80339</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>131988964</v>
       </c>
       <c r="B6" t="n">
-        <v>97287</v>
+        <v>97292</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>131988965</v>
       </c>
       <c r="B7" t="n">
-        <v>97511</v>
+        <v>97516</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 11965-2026 artfynd.xlsx
+++ b/artfynd/A 11965-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131773087</v>
       </c>
       <c r="B2" t="n">
-        <v>96488</v>
+        <v>96490</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>131775130</v>
       </c>
       <c r="B3" t="n">
-        <v>97301</v>
+        <v>97303</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>131775187</v>
       </c>
       <c r="B4" t="n">
-        <v>97387</v>
+        <v>97389</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>131988835</v>
       </c>
       <c r="B5" t="n">
-        <v>80339</v>
+        <v>80341</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>131988964</v>
       </c>
       <c r="B6" t="n">
-        <v>97292</v>
+        <v>97294</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>131988965</v>
       </c>
       <c r="B7" t="n">
-        <v>97516</v>
+        <v>97518</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 11965-2026 artfynd.xlsx
+++ b/artfynd/A 11965-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131773087</v>
       </c>
       <c r="B2" t="n">
-        <v>96490</v>
+        <v>96526</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>131775130</v>
       </c>
       <c r="B3" t="n">
-        <v>97303</v>
+        <v>97339</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>131775187</v>
       </c>
       <c r="B4" t="n">
-        <v>97389</v>
+        <v>97425</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>131988835</v>
       </c>
       <c r="B5" t="n">
-        <v>80341</v>
+        <v>80375</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>131988964</v>
       </c>
       <c r="B6" t="n">
-        <v>97294</v>
+        <v>97330</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>131988965</v>
       </c>
       <c r="B7" t="n">
-        <v>97518</v>
+        <v>97554</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 11965-2026 artfynd.xlsx
+++ b/artfynd/A 11965-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131773087</v>
       </c>
       <c r="B2" t="n">
-        <v>96526</v>
+        <v>96531</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>131775130</v>
       </c>
       <c r="B3" t="n">
-        <v>97339</v>
+        <v>97344</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>131775187</v>
       </c>
       <c r="B4" t="n">
-        <v>97425</v>
+        <v>97430</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>131988835</v>
       </c>
       <c r="B5" t="n">
-        <v>80375</v>
+        <v>80380</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>131988964</v>
       </c>
       <c r="B6" t="n">
-        <v>97330</v>
+        <v>97335</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>131988965</v>
       </c>
       <c r="B7" t="n">
-        <v>97554</v>
+        <v>97559</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 11965-2026 artfynd.xlsx
+++ b/artfynd/A 11965-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131773087</v>
       </c>
       <c r="B2" t="n">
-        <v>96531</v>
+        <v>96534</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>131775130</v>
       </c>
       <c r="B3" t="n">
-        <v>97344</v>
+        <v>97347</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>131775187</v>
       </c>
       <c r="B4" t="n">
-        <v>97430</v>
+        <v>97433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>131988835</v>
       </c>
       <c r="B5" t="n">
-        <v>80380</v>
+        <v>80382</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>131988964</v>
       </c>
       <c r="B6" t="n">
-        <v>97335</v>
+        <v>97338</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>131988965</v>
       </c>
       <c r="B7" t="n">
-        <v>97559</v>
+        <v>97562</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 11965-2026 artfynd.xlsx
+++ b/artfynd/A 11965-2026 artfynd.xlsx
@@ -1029,7 +1029,7 @@
         <v>131988835</v>
       </c>
       <c r="B5" t="n">
-        <v>80382</v>
+        <v>80384</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>131988964</v>
       </c>
       <c r="B6" t="n">
-        <v>97338</v>
+        <v>97346</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>131988965</v>
       </c>
       <c r="B7" t="n">
-        <v>97562</v>
+        <v>97570</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 11965-2026 artfynd.xlsx
+++ b/artfynd/A 11965-2026 artfynd.xlsx
@@ -1029,7 +1029,7 @@
         <v>131988835</v>
       </c>
       <c r="B5" t="n">
-        <v>80384</v>
+        <v>80392</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>131988964</v>
       </c>
       <c r="B6" t="n">
-        <v>97346</v>
+        <v>97356</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>131988965</v>
       </c>
       <c r="B7" t="n">
-        <v>97570</v>
+        <v>97580</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 11965-2026 artfynd.xlsx
+++ b/artfynd/A 11965-2026 artfynd.xlsx
@@ -1146,7 +1146,7 @@
         <v>131988964</v>
       </c>
       <c r="B6" t="n">
-        <v>97356</v>
+        <v>97358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>131988965</v>
       </c>
       <c r="B7" t="n">
-        <v>97580</v>
+        <v>97582</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 11965-2026 artfynd.xlsx
+++ b/artfynd/A 11965-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1365,6 +1365,123 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>133661114</v>
+      </c>
+      <c r="B8" t="n">
+        <v>4775</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Staverud, Lysevattnets östsida, Dls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>341517</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6521626</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Granskog med asp.</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11965-2026 artfynd.xlsx
+++ b/artfynd/A 11965-2026 artfynd.xlsx
@@ -1370,7 +1370,7 @@
         <v>133661114</v>
       </c>
       <c r="B8" t="n">
-        <v>4775</v>
+        <v>4776</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 11965-2026 artfynd.xlsx
+++ b/artfynd/A 11965-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131988964</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -906,6 +916,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131773087</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1013,6 +1028,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131988965</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1130,6 +1150,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131775130</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1247,6 +1272,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131775187</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1364,6 +1394,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131989007</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1481,6 +1516,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133661114</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1598,8 +1638,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131988835</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>